--- a/docs/dominio-metrico/migracion/cuestionarios/el-amor-al-uso.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-amor-al-uso.xlsx
@@ -21,25 +21,25 @@
     <t>Migración métrica · El amor al uso</t>
   </si>
   <si>
-    <t>Para Ana Vicente · generado el 2026-09-19</t>
-  </si>
-  <si>
-    <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, con este mismo texto. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
-  </si>
-  <si>
-    <t>En Responder están las preguntas que no hemos podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
-  </si>
-  <si>
-    <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiremos a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
-  </si>
-  <si>
-    <t>En Confirmar aparecen las respuestas que hemos rellenado nosotros a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
+    <t>Para Ana Vicente · generado el 2026-09-20</t>
+  </si>
+  <si>
+    <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
+  </si>
+  <si>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+  </si>
+  <si>
+    <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
+  </si>
+  <si>
+    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
   </si>
   <si>
     <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual. Si tienes a mano el número de sílabas de algún verso hipométrico o hipermétrico, ponlo en la columna «Sílabas»; si no, se registra simplemente que el verso tiene menos o más sílabas de las que le tocan, sin dar una cifra.</t>
   </si>
   <si>
-    <t>Si algo no está claro o no sabes cómo contestarlo, pregúntaselo a David antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y corregir allí lo que haga falta.</t>
+    <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
   </si>
   <si>
     <t>Cuando no hay desplegable, los formatos son estos:</t>

--- a/docs/dominio-metrico/migracion/cuestionarios/el-amor-al-uso.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-amor-al-uso.xlsx
@@ -33,10 +33,10 @@
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
   </si>
   <si>
-    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
-  </si>
-  <si>
-    <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual. Si tienes a mano el número de sílabas de algún verso hipométrico o hipermétrico, ponlo en la columna «Sílabas»; si no, se registra simplemente que el verso tiene menos o más sílabas de las que le tocan, sin dar una cifra.</t>
+    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Ahí van también los tramos que vuelven a ser una sola secuencia. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
+  </si>
+  <si>
+    <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual, así que basta con revisarlas: la columna «¿Correcto?» tiene el mismo desplegable que la pestaña anterior y solo hay que tocarla si algo no queda como digo. La columna «Sílabas del verso» es únicamente para los versos hipométricos e hipermétricos, por si tienes a mano cuántas sílabas mide el verso; si no la rellenas, se registra que tiene menos o más de las que le tocan, sin dar una cifra. En las demás filas esa celda está apagada.</t>
   </si>
   <si>
     <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
@@ -447,10 +447,10 @@
     <t>Cómo queda</t>
   </si>
   <si>
-    <t>Sílabas</t>
-  </si>
-  <si>
-    <t>Informativa</t>
+    <t>Sílabas del verso</t>
+  </si>
+  <si>
+    <t>Revisar</t>
   </si>
   <si>
     <t>1082</t>
@@ -2339,7 +2339,7 @@
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="44" customWidth="1"/>
     <col min="6" max="6" width="40" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
@@ -2603,6 +2603,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="H2:H8">
+      <formula1>Listas!$C$2:$C$3</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/dominio-metrico/migracion/cuestionarios/el-amor-al-uso.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-amor-al-uso.xlsx
@@ -21,7 +21,7 @@
     <t>Migración métrica · El amor al uso</t>
   </si>
   <si>
-    <t>Para Ana Vicente · generado el 2026-09-20</t>
+    <t>Para Ana Vicente · generado el 2026-09-21</t>
   </si>
   <si>
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>

--- a/docs/dominio-metrico/migracion/cuestionarios/el-amor-al-uso.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-amor-al-uso.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="208">
   <si>
     <t>Migración métrica · El amor al uso</t>
   </si>
@@ -27,7 +27,7 @@
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
   </si>
   <si>
-    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle» como «versos: esquema», por ejemplo «191-194: abab; 203-206: abab». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato.</t>
   </si>
   <si>
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
@@ -54,7 +54,7 @@
     <t>Esquema de rima: una letra por verso, en mayúscula si el verso es de arte mayor y un guion si queda suelto. Por ejemplo, «aBab-B».</t>
   </si>
   <si>
-    <t>Excepciones: los versos de la estrofa y la respuesta que le corresponde, separando cada estrofa con punto y coma. Por ejemplo, «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+    <t>Excepciones: los versos de la estrofa y su esquema, separados por dos puntos, y cada estrofa de la siguiente con punto y coma. Por ejemplo, «191-194: abab; 203-206: abab». El esquema se escribe como arriba: una letra por verso, en mayúscula si el verso es de arte mayor.</t>
   </si>
   <si>
     <t>lista</t>
@@ -141,7 +141,7 @@
     <t/>
   </si>
   <si>
-    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones» (versos: respuesta)</t>
+    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», como «191-194: abab»</t>
   </si>
   <si>
     <t>R|3912daf7-d974-4868-bc0b-df28660ebb8c|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
@@ -171,55 +171,10 @@
     <t>Quintilla · Octosílaba consonante</t>
   </si>
   <si>
-    <t>Esquema de rima · estrofa 1 (vv. 2117–2121)</t>
-  </si>
-  <si>
-    <t>Elige en el desplegable</t>
-  </si>
-  <si>
-    <t>U|07e464e4-389e-46c1-8130-6cfe0ce7694f|a43860ff-566c-4a0b-b210-4572b8d7b066|2117</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 2 (vv. 2122–2126)</t>
-  </si>
-  <si>
-    <t>U|07e464e4-389e-46c1-8130-6cfe0ce7694f|a43860ff-566c-4a0b-b210-4572b8d7b066|2122</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 3 (vv. 2127–2131)</t>
-  </si>
-  <si>
-    <t>U|07e464e4-389e-46c1-8130-6cfe0ce7694f|a43860ff-566c-4a0b-b210-4572b8d7b066|2127</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 4 (vv. 2132–2136)</t>
-  </si>
-  <si>
-    <t>U|07e464e4-389e-46c1-8130-6cfe0ce7694f|a43860ff-566c-4a0b-b210-4572b8d7b066|2132</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 5 (vv. 2137–2141)</t>
-  </si>
-  <si>
-    <t>U|07e464e4-389e-46c1-8130-6cfe0ce7694f|a43860ff-566c-4a0b-b210-4572b8d7b066|2137</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 6 (vv. 2142–2146)</t>
-  </si>
-  <si>
-    <t>U|07e464e4-389e-46c1-8130-6cfe0ce7694f|a43860ff-566c-4a0b-b210-4572b8d7b066|2142</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 7 (vv. 2147–2151)</t>
-  </si>
-  <si>
-    <t>U|07e464e4-389e-46c1-8130-6cfe0ce7694f|a43860ff-566c-4a0b-b210-4572b8d7b066|2147</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 8 (vv. 2152–2156)</t>
-  </si>
-  <si>
-    <t>U|07e464e4-389e-46c1-8130-6cfe0ce7694f|a43860ff-566c-4a0b-b210-4572b8d7b066|2152</t>
+    <t>Esquema de rima · 8 estrofas</t>
+  </si>
+  <si>
+    <t>R|07e464e4-389e-46c1-8130-6cfe0ce7694f|a43860ff-566c-4a0b-b210-4572b8d7b066</t>
   </si>
   <si>
     <t>2613–2620</t>
@@ -1292,7 +1247,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
@@ -1451,19 +1406,19 @@
         <v>40</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" s="7" t="s">
         <v>52</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1471,10 +1426,10 @@
         <v>36</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>54</v>
@@ -1483,7 +1438,7 @@
         <v>40</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>40</v>
@@ -1503,19 +1458,19 @@
         <v>36</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>40</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>40</v>
@@ -1530,244 +1485,17 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G10:G12">
-      <formula1>Listas!$B$2:$B$9</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G13:G14">
-      <formula1>Listas!$A$2:$A$3</formula1>
-    </dataValidation>
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G2:G4">
       <formula1>Listas!$A$2:$A$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G5:G12">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G5">
       <formula1>Listas!$B$2:$B$9</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G6:G7">
+      <formula1>Listas!$A$2:$A$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1799,19 +1527,19 @@
         <v>28</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>34</v>
@@ -1822,19 +1550,19 @@
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>40</v>
@@ -1846,24 +1574,24 @@
         <v>40</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>40</v>
@@ -1875,24 +1603,24 @@
         <v>40</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>40</v>
@@ -1904,24 +1632,24 @@
         <v>40</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>40</v>
@@ -1933,24 +1661,24 @@
         <v>40</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>40</v>
@@ -1962,24 +1690,24 @@
         <v>40</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>40</v>
@@ -1991,24 +1719,24 @@
         <v>40</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>40</v>
@@ -2020,24 +1748,24 @@
         <v>40</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>40</v>
@@ -2049,24 +1777,24 @@
         <v>40</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>40</v>
@@ -2078,24 +1806,24 @@
         <v>40</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>40</v>
@@ -2107,24 +1835,24 @@
         <v>40</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>40</v>
@@ -2136,24 +1864,24 @@
         <v>40</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>40</v>
@@ -2165,24 +1893,24 @@
         <v>40</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>40</v>
@@ -2194,24 +1922,24 @@
         <v>40</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>40</v>
@@ -2223,24 +1951,24 @@
         <v>40</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>40</v>
@@ -2252,24 +1980,24 @@
         <v>40</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>40</v>
@@ -2281,24 +2009,24 @@
         <v>40</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>40</v>
@@ -2310,7 +2038,7 @@
         <v>40</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -2353,22 +2081,22 @@
         <v>27</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>34</v>
@@ -2379,22 +2107,22 @@
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>40</v>
@@ -2406,27 +2134,27 @@
         <v>40</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>40</v>
@@ -2438,28 +2166,28 @@
         <v>40</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>159</v>
-      </c>
       <c r="G4" s="8" t="s">
         <v>40</v>
       </c>
@@ -2470,27 +2198,27 @@
         <v>40</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>40</v>
@@ -2502,27 +2230,27 @@
         <v>40</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>40</v>
@@ -2534,27 +2262,27 @@
         <v>40</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>40</v>
@@ -2566,27 +2294,27 @@
         <v>40</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="C8" s="3" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>40</v>
@@ -2598,7 +2326,7 @@
         <v>40</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -2633,37 +2361,37 @@
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>28</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>30</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2677,28 +2405,28 @@
         <v>20</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2706,34 +2434,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="C3" s="3">
         <v>24</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2747,28 +2475,28 @@
         <v>80</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2776,34 +2504,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="C5" s="3">
         <v>296</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2811,34 +2539,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="C6" s="3">
         <v>30</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2852,28 +2580,28 @@
         <v>48</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2881,34 +2609,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C8" s="3">
         <v>216</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2916,34 +2644,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="C9" s="3">
         <v>10</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2951,34 +2679,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C10" s="3">
         <v>318</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2986,34 +2714,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="C11" s="3">
         <v>75</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3021,34 +2749,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="C12" s="3">
         <v>56</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3056,34 +2784,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="C13" s="3">
         <v>174</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3091,34 +2819,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C14" s="3">
         <v>60</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3126,34 +2854,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="C15" s="3">
         <v>130</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3161,34 +2889,34 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="C16" s="3">
         <v>192</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3196,34 +2924,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C17" s="3">
         <v>308</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3231,34 +2959,34 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="C18" s="3">
         <v>65</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>216</v>
-      </c>
       <c r="K18" s="3" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3266,34 +2994,34 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="C19" s="3">
         <v>14</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3307,28 +3035,28 @@
         <v>40</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3336,34 +3064,34 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="C21" s="3">
         <v>388</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3371,34 +3099,34 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C22" s="3">
         <v>68</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3406,34 +3134,34 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="C23" s="3">
         <v>8</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3441,34 +3169,34 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="C24" s="3">
         <v>24</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3476,34 +3204,34 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="C25" s="3">
         <v>108</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3511,34 +3239,34 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="C26" s="3">
         <v>48</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3546,34 +3274,34 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="C27" s="3">
         <v>124</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3581,34 +3309,34 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="C28" s="3">
         <v>50</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3616,34 +3344,34 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="C29" s="3">
         <v>82</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/docs/dominio-metrico/migracion/cuestionarios/el-amor-al-uso.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-amor-al-uso.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="203">
   <si>
     <t>Migración métrica · El amor al uso</t>
   </si>
@@ -27,7 +27,7 @@
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
   </si>
   <si>
-    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle» como «versos: esquema», por ejemplo «191-194: abab; 203-206: abab». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato.</t>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» dice el formato y da un ejemplo.</t>
   </si>
   <si>
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
@@ -42,21 +42,6 @@
     <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
   </si>
   <si>
-    <t>Cuando no hay desplegable, los formatos son estos:</t>
-  </si>
-  <si>
-    <t>Medidas: el número de sílabas de cada verso, en orden y separados por espacios. Por ejemplo, «7 11 7 7 11 7 11 11».</t>
-  </si>
-  <si>
-    <t>Posiciones: en qué versos de la estrofa cae el quebrado y cuántas sílabas tiene cada uno, separados por comas. Por ejemplo, «3: 4, 8: 5» quiere decir que el verso 3 tiene cuatro sílabas y el 8 tiene cinco.</t>
-  </si>
-  <si>
-    <t>Esquema de rima: una letra por verso, en mayúscula si el verso es de arte mayor y un guion si queda suelto. Por ejemplo, «aBab-B».</t>
-  </si>
-  <si>
-    <t>Excepciones: los versos de la estrofa y su esquema, separados por dos puntos, y cada estrofa de la siguiente con punto y coma. Por ejemplo, «191-194: abab; 203-206: abab». El esquema se escribe como arriba: una letra por verso, en mayúscula si el verso es de arte mayor.</t>
-  </si>
-  <si>
     <t>lista</t>
   </si>
   <si>
@@ -141,7 +126,7 @@
     <t/>
   </si>
   <si>
-    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», como «191-194: abab»</t>
+    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», una detrás de otra y separadas por punto y coma, como «191-194: abab; 203-206: abab»</t>
   </si>
   <si>
     <t>R|3912daf7-d974-4868-bc0b-df28660ebb8c|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
@@ -732,14 +717,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1091,7 +1075,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -1135,31 +1119,6 @@
     <row r="9" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1178,65 +1137,65 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1261,228 +1220,228 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="G2" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="G3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>48</v>
+      <c r="G4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>52</v>
+      <c r="G5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>55</v>
+      <c r="G6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>57</v>
+      <c r="G7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1519,526 +1478,526 @@
     <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>35</v>
+      <c r="E1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>73</v>
+        <v>67</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>75</v>
+        <v>67</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>80</v>
+        <v>74</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>84</v>
+        <v>78</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" s="6" t="s">
         <v>85</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>94</v>
+        <v>88</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>97</v>
+        <v>74</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>101</v>
+        <v>95</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>111</v>
+        <v>105</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>113</v>
+        <v>84</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>115</v>
+        <v>84</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>119</v>
+        <v>113</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>121</v>
+        <v>67</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>123</v>
+        <v>67</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -2073,260 +2032,260 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>35</v>
+    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="G2" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>130</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="G5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>157</v>
+        <v>151</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>160</v>
+      <c r="G7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>162</v>
+        <v>151</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -2359,39 +2318,39 @@
     <col min="11" max="11" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="J1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>164</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2399,34 +2358,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C2" s="3">
         <v>20</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2434,34 +2393,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C3" s="3">
         <v>24</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="K3" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2469,34 +2428,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C4" s="3">
         <v>80</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2504,34 +2463,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C5" s="3">
         <v>296</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="K5" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2539,34 +2498,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C6" s="3">
         <v>30</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2574,34 +2533,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C7" s="3">
         <v>48</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2609,34 +2568,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C8" s="3">
         <v>216</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="K8" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2644,34 +2603,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C9" s="3">
         <v>10</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2679,34 +2638,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C10" s="3">
         <v>318</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="K10" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2714,34 +2673,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C11" s="3">
         <v>75</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>192</v>
-      </c>
       <c r="K11" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2749,34 +2708,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C12" s="3">
         <v>56</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2784,34 +2743,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C13" s="3">
         <v>174</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G13" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="K13" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2819,34 +2778,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C14" s="3">
         <v>60</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="G14" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="K14" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2854,34 +2813,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C15" s="3">
         <v>130</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G15" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="K15" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2889,34 +2848,34 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C16" s="3">
         <v>192</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2924,34 +2883,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C17" s="3">
         <v>308</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G17" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="K17" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2959,34 +2918,34 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C18" s="3">
         <v>65</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>191</v>
-      </c>
       <c r="J18" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2994,34 +2953,34 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C19" s="3">
         <v>14</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3029,34 +2988,34 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C20" s="3">
         <v>40</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3064,34 +3023,34 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C21" s="3">
         <v>388</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="K21" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3099,34 +3058,34 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C22" s="3">
         <v>68</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="G22" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="K22" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3134,34 +3093,34 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C23" s="3">
         <v>8</v>
       </c>
       <c r="D23" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="K23" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3169,34 +3128,34 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C24" s="3">
         <v>24</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="G24" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="K24" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3204,34 +3163,34 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C25" s="3">
         <v>108</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G25" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J25" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="K25" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3239,34 +3198,34 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C26" s="3">
         <v>48</v>
       </c>
       <c r="D26" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="K26" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="27" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3274,34 +3233,34 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C27" s="3">
         <v>124</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G27" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="K27" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3309,34 +3268,34 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C28" s="3">
         <v>50</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="29" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3344,34 +3303,34 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C29" s="3">
         <v>82</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G29" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="K29" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
